--- a/AtchisonRegime/Outputs/USA/USA500_Materials/df_regSummary_USA500_Materials.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Materials/df_regSummary_USA500_Materials.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.473376362221011</v>
+        <v>1.453965102335928</v>
       </c>
       <c r="H2" t="n">
-        <v>3.612573251183403</v>
+        <v>3.586631954839385</v>
       </c>
       <c r="I2" t="n">
         <v>-6.119052067979229</v>
@@ -545,16 +545,16 @@
         <v>10.2371026217823</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2161631940696445</v>
+        <v>0.2167319629055521</v>
       </c>
       <c r="O2" t="n">
         <v>-0.02919700639085454</v>
@@ -603,7 +603,7 @@
         <v>9.97010822270626</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>11.7139405168735</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>9.589243507641781</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
